--- a/data/trans_camb/P2C_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,72</t>
+          <t>-0,98; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,89</t>
+          <t>0,08; 3,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,99; 34,94</t>
+          <t>18,72; 33,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,87</t>
+          <t>-0,43; 1,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,64</t>
+          <t>-1,01; 0,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 32,55</t>
+          <t>21,61; 31,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,18</t>
+          <t>-0,42; 1,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,48</t>
+          <t>-0,24; 1,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,49; 30,5</t>
+          <t>21,5; 31,02</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,6; —</t>
+          <t>-70,58; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1379,11; —</t>
+          <t>1332,45; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1373,24; —</t>
+          <t>1523,09; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 803,56</t>
+          <t>-61,37; 713,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 980,34</t>
+          <t>-48,52; 770,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2041,08; 21183,17</t>
+          <t>2073,19; 21276,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,6</t>
+          <t>-1,46; 0,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,66</t>
+          <t>-1,7; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 19,99</t>
+          <t>8,79; 20,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,49</t>
+          <t>-1,77; 0,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,68</t>
+          <t>-1,73; 0,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 17,98</t>
+          <t>10,83; 18,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,26</t>
+          <t>-1,29; 0,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,39</t>
+          <t>-1,29; 0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,49</t>
+          <t>11,0; 17,29</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 477,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430,37; 8631,86</t>
+          <t>422,92; 8419,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,65; 171,47</t>
+          <t>-86,55; 134,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>516,29; 3214,05</t>
+          <t>498,77; 3558,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,96; 62,35</t>
+          <t>-83,19; 72,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 88,65</t>
+          <t>-82,08; 73,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>736,77; 3592,77</t>
+          <t>684,73; 3213,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,85</t>
+          <t>0,22; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 23,8</t>
+          <t>9,05; 24,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,85</t>
+          <t>-0,63; 1,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,9</t>
+          <t>-0,65; 1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 11,85</t>
+          <t>-0,16; 12,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,66</t>
+          <t>-0,11; 1,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,42</t>
+          <t>-0,14; 1,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 13,95</t>
+          <t>1,71; 14,24</t>
         </is>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,94; —</t>
+          <t>-77,64; 830,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 2756,09</t>
+          <t>-18,62; 2553,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 1520,38</t>
+          <t>-46,41; 1226,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 1124,03</t>
+          <t>-43,29; 1060,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>235,23; 6363,1</t>
+          <t>218,32; 7978,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,76</t>
+          <t>-1,02; 1,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,48</t>
+          <t>-0,81; 1,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 18,57</t>
+          <t>7,4; 19,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,43</t>
+          <t>-0,12; 2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,77</t>
+          <t>-0,46; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,8; 22,15</t>
+          <t>12,87; 21,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,55</t>
+          <t>-0,22; 1,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,35</t>
+          <t>-0,34; 1,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 18,51</t>
+          <t>11,51; 18,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-78,63; 544,37</t>
+          <t>-84,41; 566,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,84; 409,23</t>
+          <t>-72,87; 472,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>469,16; 4453,49</t>
+          <t>459,86; 4334,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 977,85</t>
+          <t>-27,81; 1056,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 788,97</t>
+          <t>-50,29; 966,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>796,19; 9398,42</t>
+          <t>886,87; 10658,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 370,03</t>
+          <t>-26,9; 343,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 295,78</t>
+          <t>-40,05; 337,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>858,58; 3938,36</t>
+          <t>912,73; 4231,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,73</t>
+          <t>-0,3; 0,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,95</t>
+          <t>-0,21; 0,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,43</t>
+          <t>13,05; 19,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,95</t>
+          <t>-0,29; 0,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,84</t>
+          <t>-0,34; 0,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 17,39</t>
+          <t>6,51; 17,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,16; 0,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,18; 0,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,05</t>
+          <t>7,8; 17,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 206,99</t>
+          <t>-41,25; 237,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 292,54</t>
+          <t>-31,9; 262,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1334,07; 5507,74</t>
+          <t>1426,03; 5527,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 198,03</t>
+          <t>-29,81; 190,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 172,11</t>
+          <t>-34,69; 166,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>634,53; 2977,19</t>
+          <t>660,06; 2867,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 139,92</t>
+          <t>-18,2; 136,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 133,0</t>
+          <t>-20,02; 137,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1052,54; 3156,47</t>
+          <t>1063,87; 3273,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,64</t>
+          <t>24,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,34</t>
+          <t>26,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26,04</t>
+          <t>25,4</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,93</t>
+          <t>-0,98; 0,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,01</t>
+          <t>0,01; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,72; 33,57</t>
+          <t>17,83; 33,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,96</t>
+          <t>-0,39; 1,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,79</t>
+          <t>-1,0; 0,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,61; 31,64</t>
+          <t>20,91; 31,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,13</t>
+          <t>-0,33; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,47</t>
+          <t>-0,16; 1,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,5; 31,02</t>
+          <t>20,33; 29,71</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5263,86%</t>
+          <t>5041,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5559,82%</t>
+          <t>5491,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5426,35%</t>
+          <t>5292,01%</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-70,58; —</t>
+          <t>-61,22; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1332,45; —</t>
+          <t>1329,89; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1523,09; —</t>
+          <t>1587,01; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 713,26</t>
+          <t>-57,66; 602,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 770,98</t>
+          <t>-36,61; 833,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2073,19; 21276,31</t>
+          <t>2046,96; 20528,27</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>13,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>12,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,58</t>
+          <t>-1,62; 0,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,59</t>
+          <t>-1,62; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 20,47</t>
+          <t>7,72; 18,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,48</t>
+          <t>-1,65; 0,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,63</t>
+          <t>-1,67; 0,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 18,09</t>
+          <t>10,45; 17,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,32</t>
+          <t>-1,25; 0,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,34</t>
+          <t>-1,2; 0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,29</t>
+          <t>10,41; 16,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1698,75%</t>
+          <t>1508,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1259,64%</t>
+          <t>1197,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1438,44%</t>
+          <t>1329,45%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 477,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422,92; 8419,78</t>
+          <t>294,28; 7913,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,55; 134,95</t>
+          <t>-83,85; 177,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>498,77; 3558,17</t>
+          <t>450,39; 3404,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 72,16</t>
+          <t>-83,14; 88,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 73,34</t>
+          <t>-79,62; 99,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>684,73; 3213,16</t>
+          <t>645,45; 2936,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>12,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,79</t>
+          <t>0,4; 2,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 24,16</t>
+          <t>8,15; 22,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,94</t>
+          <t>-0,71; 1,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,86</t>
+          <t>-0,63; 2,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 12,47</t>
+          <t>7,02; 15,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,69</t>
+          <t>0,01; 1,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,36</t>
+          <t>-0,11; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,24</t>
+          <t>8,65; 16,24</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>550,32%</t>
+          <t>1617,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1818,05%</t>
+          <t>3380,74%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,72; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,64; 830,53</t>
+          <t>-72,78; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 2553,26</t>
+          <t>465,38; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,41; 1226,79</t>
+          <t>-22,69; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,29; 1060,3</t>
+          <t>-51,47; 1078,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218,32; 7978,85</t>
+          <t>1086,44; 14462,63</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,12</t>
+          <t>10,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,77</t>
+          <t>15,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,87</t>
+          <t>13,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,61</t>
+          <t>-0,86; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,62</t>
+          <t>-0,78; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 19,08</t>
+          <t>6,17; 16,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,33</t>
+          <t>-0,09; 2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,87</t>
+          <t>-0,53; 1,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,87; 21,76</t>
+          <t>11,83; 21,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,56</t>
+          <t>-0,13; 1,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,48</t>
+          <t>-0,37; 1,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,51; 18,79</t>
+          <t>10,35; 17,19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1401,4%</t>
+          <t>1239,63%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2329,26%</t>
+          <t>2171,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1903,84%</t>
+          <t>1749,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,41; 566,62</t>
+          <t>-76,48; 459,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 472,94</t>
+          <t>-62,11; 502,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>459,86; 4334,6</t>
+          <t>440,32; 4258,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 1056,66</t>
+          <t>-29,47; 931,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 966,73</t>
+          <t>-58,54; 751,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>886,87; 10658,68</t>
+          <t>723,77; 8975,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,9; 343,7</t>
+          <t>-23,57; 361,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 337,59</t>
+          <t>-35,95; 314,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>912,73; 4231,44</t>
+          <t>811,54; 4076,75</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,64</t>
+          <t>15,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>15,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,79</t>
+          <t>-0,38; 0,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,9</t>
+          <t>-0,25; 0,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,05; 19,76</t>
+          <t>11,95; 18,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,96</t>
+          <t>-0,2; 1,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,8</t>
+          <t>-0,38; 0,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 17,38</t>
+          <t>13,85; 17,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,68</t>
+          <t>-0,09; 0,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,66</t>
+          <t>-0,12; 0,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,8; 17,09</t>
+          <t>13,68; 17,29</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2772,29%</t>
+          <t>2513,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1641,36%</t>
+          <t>2063,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2028,51%</t>
+          <t>2244,72%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 237,38</t>
+          <t>-45,78; 232,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 262,82</t>
+          <t>-38,34; 311,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1426,03; 5527,47</t>
+          <t>1172,66; 5418,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 190,34</t>
+          <t>-25,37; 211,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 166,19</t>
+          <t>-35,7; 150,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>660,06; 2867,39</t>
+          <t>1197,08; 3695,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 136,33</t>
+          <t>-10,37; 148,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 137,04</t>
+          <t>-14,8; 143,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1063,87; 3273,38</t>
+          <t>1480,24; 3585,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
